--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008423898014371441</v>
       </c>
       <c r="C2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>18941726</v>
+        <v>4487784</v>
       </c>
       <c r="L2" t="n">
-        <v>11535571</v>
+        <v>2532219</v>
       </c>
       <c r="M2" t="n">
-        <v>2993614</v>
+        <v>611068</v>
       </c>
       <c r="N2" t="n">
-        <v>168455</v>
+        <v>23499</v>
       </c>
       <c r="O2" t="n">
-        <v>1747825</v>
+        <v>373161</v>
       </c>
       <c r="P2" t="n">
-        <v>681614</v>
+        <v>149489</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999665021896362</v>
+        <v>0.9999383687973022</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9382599592208862</v>
+        <v>0.8818544745445251</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8591461777687073</v>
+        <v>0.7575032711029053</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8293046355247498</v>
+        <v>0.6902445554733276</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5960350632667542</v>
+        <v>0.3172539472579956</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8641053438186646</v>
+        <v>0.7487900257110596</v>
       </c>
       <c r="W2" t="n">
-        <v>0.911750853061676</v>
+        <v>0.8321772813796997</v>
       </c>
       <c r="X2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566585421562195</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911242663860321</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581098318099976</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624432802200317</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020154476165771</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00201873763595948</v>
       </c>
       <c r="C3" t="n">
-        <v>560</v>
+        <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>18941726</v>
+        <v>4487784</v>
       </c>
       <c r="E3" t="n">
-        <v>1309146</v>
+        <v>562183</v>
       </c>
       <c r="F3" t="n">
-        <v>12157</v>
+        <v>6940</v>
       </c>
       <c r="G3" t="n">
-        <v>1842</v>
+        <v>774</v>
       </c>
       <c r="H3" t="n">
-        <v>604</v>
+        <v>361</v>
       </c>
       <c r="I3" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>40277629</v>
+        <v>10069229</v>
       </c>
       <c r="K3" t="n">
-        <v>44151497</v>
+        <v>10756494</v>
       </c>
       <c r="L3" t="n">
-        <v>50663341</v>
+        <v>12320834</v>
       </c>
       <c r="M3" t="n">
-        <v>61312376</v>
+        <v>15207256</v>
       </c>
       <c r="N3" t="n">
-        <v>65192668</v>
+        <v>16276056</v>
       </c>
       <c r="O3" t="n">
-        <v>63351980</v>
+        <v>15781224</v>
       </c>
       <c r="P3" t="n">
-        <v>64824834</v>
+        <v>16192507</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9346514344215393</v>
+        <v>0.8872189521789551</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8799434900283813</v>
+        <v>0.7709518074989319</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8014065027236938</v>
+        <v>0.6538843512535095</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4716500341892242</v>
+        <v>0.262931764125824</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8579772710800171</v>
+        <v>0.7322841286659241</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8815585374832153</v>
+        <v>0.7731683254241943</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>796241</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34282</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27251</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40278480</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44518633</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51392586</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61398817</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65186364</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63427333</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64837792</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576596021652222</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099968671798706</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576393723487854</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619647741317749</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016187191009521</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,130 +926,130 @@
         <v>0.03188454573346271</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1176659</v>
+        <v>569785</v>
       </c>
       <c r="E4" t="n">
-        <v>11535571</v>
+        <v>2532219</v>
       </c>
       <c r="F4" t="n">
-        <v>370221</v>
+        <v>166014</v>
       </c>
       <c r="G4" t="n">
-        <v>8879</v>
+        <v>5092</v>
       </c>
       <c r="H4" t="n">
-        <v>17080</v>
+        <v>10726</v>
       </c>
       <c r="I4" t="n">
-        <v>1033</v>
+        <v>699</v>
       </c>
       <c r="J4" t="n">
-        <v>851</v>
+        <v>391</v>
       </c>
       <c r="K4" t="n">
-        <v>1246417</v>
+        <v>601246</v>
       </c>
       <c r="L4" t="n">
-        <v>1891214</v>
+        <v>810630</v>
       </c>
       <c r="M4" t="n">
-        <v>616174</v>
+        <v>274224</v>
       </c>
       <c r="N4" t="n">
-        <v>114171</v>
+        <v>50571</v>
       </c>
       <c r="O4" t="n">
-        <v>274874</v>
+        <v>125191</v>
       </c>
       <c r="P4" t="n">
-        <v>65974</v>
+        <v>30147</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999832510948181</v>
+        <v>0.9999691843986511</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9364522099494934</v>
+        <v>0.8845285177230835</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8694204688072205</v>
+        <v>0.764168381690979</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8151170015335083</v>
+        <v>0.6715726852416992</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5265971422195435</v>
+        <v>0.2875497937202454</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8610303997993469</v>
+        <v>0.740445077419281</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8964004516601562</v>
+        <v>0.8015882968902588</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>820988</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332033</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22018</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>879281</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1161969</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>529733</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120475</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199521</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571588635444641</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106193780899048</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578745126724243</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622039079666138</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018170833587646</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>170</v>
       </c>
       <c r="D5" t="n">
-        <v>42156</v>
+        <v>19475</v>
       </c>
       <c r="E5" t="n">
-        <v>506870</v>
+        <v>217410</v>
       </c>
       <c r="F5" t="n">
-        <v>2993614</v>
+        <v>611068</v>
       </c>
       <c r="G5" t="n">
-        <v>45639</v>
+        <v>19129</v>
       </c>
       <c r="H5" t="n">
-        <v>140013</v>
+        <v>62925</v>
       </c>
       <c r="I5" t="n">
-        <v>6988</v>
+        <v>4343</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1324360</v>
+        <v>570476</v>
       </c>
       <c r="L5" t="n">
-        <v>1573874</v>
+        <v>752317</v>
       </c>
       <c r="M5" t="n">
-        <v>741836</v>
+        <v>323452</v>
       </c>
       <c r="N5" t="n">
-        <v>188706</v>
+        <v>65874</v>
       </c>
       <c r="O5" t="n">
-        <v>289321</v>
+        <v>136424</v>
       </c>
       <c r="P5" t="n">
-        <v>91578</v>
+        <v>43857</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999870657920837</v>
+        <v>0.9999761581420898</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9608495235443115</v>
+        <v>0.9286231994628906</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9472300410270691</v>
+        <v>0.9047912359237671</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9793187975883484</v>
+        <v>0.9635918736457825</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9953874945640564</v>
+        <v>0.9929066300392151</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9914078712463379</v>
+        <v>0.9840633869171143</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976006150245667</v>
+        <v>0.9954919815063477</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32176</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>340707</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39817</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116549</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>858074</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1179891</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>531781</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120733</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200417</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735417366027832</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643356800079346</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838341474533081</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939092993736267</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983839988708496</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>27485</v>
+        <v>11948</v>
       </c>
       <c r="E6" t="n">
-        <v>56692</v>
+        <v>18487</v>
       </c>
       <c r="F6" t="n">
-        <v>70215</v>
+        <v>23135</v>
       </c>
       <c r="G6" t="n">
-        <v>168455</v>
+        <v>23499</v>
       </c>
       <c r="H6" t="n">
-        <v>32363</v>
+        <v>11424</v>
       </c>
       <c r="I6" t="n">
-        <v>1893</v>
+        <v>861</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25894</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21451</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43534</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27930</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>17661</v>
+        <v>12010</v>
       </c>
       <c r="F7" t="n">
-        <v>159521</v>
+        <v>75604</v>
       </c>
       <c r="G7" t="n">
-        <v>56064</v>
+        <v>24575</v>
       </c>
       <c r="H7" t="n">
-        <v>1747825</v>
+        <v>373161</v>
       </c>
       <c r="I7" t="n">
-        <v>56009</v>
+        <v>24221</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3246</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118564</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30328</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>845</v>
+        <v>540</v>
       </c>
       <c r="F8" t="n">
-        <v>4060</v>
+        <v>2531</v>
       </c>
       <c r="G8" t="n">
-        <v>1747</v>
+        <v>1001</v>
       </c>
       <c r="H8" t="n">
-        <v>84814</v>
+        <v>39755</v>
       </c>
       <c r="I8" t="n">
-        <v>681614</v>
+        <v>149489</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
